--- a/data/trans_dic/IP16A02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 41,51</t>
+          <t>15,49; 41,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,54; 61,53</t>
+          <t>37,72; 61,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,79; 46,49</t>
+          <t>21,03; 47,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,03; 71,3</t>
+          <t>36,53; 72,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,16; 55,57</t>
+          <t>26,77; 55,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,33; 49,87</t>
+          <t>28,36; 50,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,44; 54,23</t>
+          <t>25,94; 53,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,78; 57,97</t>
+          <t>29,45; 60,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,45; 44,62</t>
+          <t>25,18; 44,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,07; 52,35</t>
+          <t>36,03; 51,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,67; 45,63</t>
+          <t>26,29; 46,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,65; 60,46</t>
+          <t>36,67; 60,44</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,55; 45,06</t>
+          <t>22,18; 46,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 40,73</t>
+          <t>21,64; 41,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,39; 52,67</t>
+          <t>30,0; 52,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,94; 59,19</t>
+          <t>33,57; 59,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,41; 57,93</t>
+          <t>35,64; 57,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,25; 46,68</t>
+          <t>28,53; 47,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,82; 46,32</t>
+          <t>24,54; 46,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,94; 60,18</t>
+          <t>36,11; 59,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,44; 48,43</t>
+          <t>32,01; 47,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,81; 41,27</t>
+          <t>27,26; 40,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,99; 46,62</t>
+          <t>30,06; 46,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,47; 56,66</t>
+          <t>37,44; 56,0</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 48,0</t>
+          <t>16,63; 48,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,47; 57,83</t>
+          <t>31,67; 58,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,1; 40,48</t>
+          <t>18,31; 41,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,95; 73,3</t>
+          <t>46,11; 73,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,33; 50,73</t>
+          <t>21,55; 52,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,39; 55,6</t>
+          <t>27,58; 57,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,32; 51,38</t>
+          <t>25,23; 50,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,42; 56,97</t>
+          <t>32,16; 58,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,41; 44,3</t>
+          <t>21,94; 45,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,71; 53,14</t>
+          <t>33,86; 53,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,56; 41,57</t>
+          <t>25,65; 42,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,3; 60,68</t>
+          <t>41,12; 60,89</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,77; 53,76</t>
+          <t>26,27; 54,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,97; 63,44</t>
+          <t>35,0; 62,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,89; 65,71</t>
+          <t>36,46; 64,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 41,61</t>
+          <t>7,2; 41,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,89; 52,5</t>
+          <t>27,22; 52,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,55; 54,42</t>
+          <t>27,6; 55,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,98; 50,42</t>
+          <t>20,67; 50,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,06; 54,54</t>
+          <t>29,63; 54,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 48,9</t>
+          <t>30,53; 49,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,41; 55,76</t>
+          <t>35,04; 53,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,02; 54,69</t>
+          <t>33,96; 54,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 43,38</t>
+          <t>17,94; 44,07</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,2; 40,04</t>
+          <t>25,9; 39,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,18; 47,32</t>
+          <t>36,17; 47,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,13; 45,07</t>
+          <t>32,81; 45,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,21; 50,31</t>
+          <t>24,32; 50,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,93; 47,9</t>
+          <t>34,86; 47,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,35; 45,05</t>
+          <t>33,53; 44,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,62; 44,17</t>
+          <t>30,69; 43,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,44; 50,87</t>
+          <t>37,46; 50,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,06; 42,15</t>
+          <t>32,53; 42,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,21; 44,92</t>
+          <t>36,28; 44,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,52; 42,23</t>
+          <t>33,53; 42,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,13; 48,3</t>
+          <t>32,5; 47,98</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10056</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8629</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20083</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11885</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9659</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>19977</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>44951</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21940</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>18288</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4498; 12173</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18671; 30634</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6580; 14786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5839; 11559</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7939; 16423</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>14675; 26364</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7828; 16125</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6585; 13529</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>14779; 26040</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36484; 52176</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16163; 28361</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>14058; 23171</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>14295</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19933</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21807</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23461</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28521</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16420</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>23264</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>37757</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>48453</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38228</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>44980</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>9587; 20171</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14121; 26830</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15545; 27049</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>15652; 27531</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>18162; 29293</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21657; 36144</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11624; 22114</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>17687; 29078</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>30149; 45160</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>38484; 57083</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>29815; 45943</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>35798; 53545</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6703</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16742</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12756</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22793</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8489</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13467</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16593</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>20080</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15192</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>30210</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29348</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>42873</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3743; 10837</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11948; 22174</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8039; 18078</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17131; 27265</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5142; 12619</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8960; 18599</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10799; 21567</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14847; 26843</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10174; 20963</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>23780; 37617</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22240; 37220</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>34262; 50731</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12343</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17168</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18553</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18378</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15370</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9255</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>27093</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>27713</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30296</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27808</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>45471</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>8022; 16764</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12305; 22148</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13211; 23226</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5609; 32605</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10736; 20750</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8988; 18059</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5588; 13657</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>19169; 35303</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>21366; 34600</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>23731; 36248</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>21489; 34505</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>25592; 62860</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>41295</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>78711</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>63172</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>59343</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>100638</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>153910</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>117324</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>151613</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>32457; 49838</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>67876; 89891</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>53571; 73725</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>43225; 89984</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>50167; 68950</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>64620; 86300</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>45230; 63813</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>68245; 92357</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>87583; 113508</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>138008; 171072</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>104160; 132584</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>116988; 172684</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 41,92</t>
+          <t>16,22; 41,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,72; 61,88</t>
+          <t>38,22; 61,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 47,25</t>
+          <t>20,57; 46,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 72,32</t>
+          <t>34,91; 71,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,77; 55,38</t>
+          <t>26,8; 54,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,36; 50,95</t>
+          <t>27,55; 50,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,94; 53,43</t>
+          <t>26,68; 54,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,45; 60,51</t>
+          <t>30,42; 60,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,18; 44,37</t>
+          <t>24,68; 44,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,03; 51,53</t>
+          <t>36,29; 53,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,29; 46,14</t>
+          <t>26,12; 45,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,67; 60,44</t>
+          <t>36,52; 60,24</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,18; 46,67</t>
+          <t>22,72; 45,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,64; 41,12</t>
+          <t>21,41; 39,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,0; 52,19</t>
+          <t>30,93; 52,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,57; 59,05</t>
+          <t>33,82; 58,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,64; 57,48</t>
+          <t>35,58; 56,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,53; 47,62</t>
+          <t>27,77; 47,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,54; 46,69</t>
+          <t>24,23; 45,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,11; 59,36</t>
+          <t>35,16; 59,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,01; 47,95</t>
+          <t>31,73; 48,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,26; 40,44</t>
+          <t>27,6; 40,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,06; 46,32</t>
+          <t>31,1; 46,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,44; 56,0</t>
+          <t>37,98; 55,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,63; 48,15</t>
+          <t>16,04; 46,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,67; 58,77</t>
+          <t>31,51; 56,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,31; 41,18</t>
+          <t>18,36; 40,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,11; 73,39</t>
+          <t>47,89; 73,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,55; 52,87</t>
+          <t>19,93; 51,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,58; 57,24</t>
+          <t>26,95; 56,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,23; 50,39</t>
+          <t>27,36; 51,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,16; 58,14</t>
+          <t>30,25; 58,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,94; 45,2</t>
+          <t>23,12; 44,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,86; 53,57</t>
+          <t>33,85; 53,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,65; 42,93</t>
+          <t>26,09; 43,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,12; 60,89</t>
+          <t>42,35; 60,88</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,27; 54,89</t>
+          <t>25,85; 54,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,0; 62,99</t>
+          <t>36,34; 63,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,46; 64,09</t>
+          <t>38,0; 65,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 41,82</t>
+          <t>7,83; 41,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,22; 52,61</t>
+          <t>27,19; 51,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,6; 55,46</t>
+          <t>28,0; 55,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,67; 50,5</t>
+          <t>20,98; 50,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,63; 54,57</t>
+          <t>29,64; 53,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,53; 49,44</t>
+          <t>30,04; 48,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,04; 53,52</t>
+          <t>34,29; 54,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,96; 54,53</t>
+          <t>34,36; 55,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,94; 44,07</t>
+          <t>16,33; 42,88</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,9; 39,77</t>
+          <t>26,9; 40,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,17; 47,91</t>
+          <t>35,84; 48,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,81; 45,16</t>
+          <t>32,48; 44,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,32; 50,63</t>
+          <t>24,68; 50,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,86; 47,91</t>
+          <t>35,37; 47,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 44,78</t>
+          <t>33,24; 45,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,69; 43,3</t>
+          <t>30,42; 43,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,46; 50,69</t>
+          <t>36,84; 50,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,53; 42,16</t>
+          <t>33,17; 42,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,28; 44,98</t>
+          <t>36,45; 45,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 42,68</t>
+          <t>33,28; 42,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,5; 47,98</t>
+          <t>31,55; 47,77</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4498; 12173</t>
+          <t>4710; 12077</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18671; 30634</t>
+          <t>18919; 30644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6580; 14786</t>
+          <t>6438; 14638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5839; 11559</t>
+          <t>5580; 11506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7939; 16423</t>
+          <t>7947; 16205</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14675; 26364</t>
+          <t>14257; 26334</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7828; 16125</t>
+          <t>8051; 16569</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6585; 13529</t>
+          <t>6801; 13533</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14779; 26040</t>
+          <t>14487; 26008</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36484; 52176</t>
+          <t>36742; 53770</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16163; 28361</t>
+          <t>16057; 27976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14058; 23171</t>
+          <t>14003; 23097</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9587; 20171</t>
+          <t>9821; 19762</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14121; 26830</t>
+          <t>13968; 25969</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15545; 27049</t>
+          <t>16031; 27085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15652; 27531</t>
+          <t>15769; 27463</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18162; 29293</t>
+          <t>18132; 28672</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21657; 36144</t>
+          <t>21076; 35986</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11624; 22114</t>
+          <t>11475; 21782</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17687; 29078</t>
+          <t>17222; 29298</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30149; 45160</t>
+          <t>29879; 45514</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38484; 57083</t>
+          <t>38956; 57659</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29815; 45943</t>
+          <t>30845; 46021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35798; 53545</t>
+          <t>36316; 53469</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3743; 10837</t>
+          <t>3611; 10559</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11948; 22174</t>
+          <t>11887; 21310</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8039; 18078</t>
+          <t>8059; 17861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17131; 27265</t>
+          <t>17791; 27379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5142; 12619</t>
+          <t>4757; 12234</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8960; 18599</t>
+          <t>8757; 18292</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10799; 21567</t>
+          <t>11709; 22044</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14847; 26843</t>
+          <t>13967; 26800</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10174; 20963</t>
+          <t>10722; 20696</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23780; 37617</t>
+          <t>23772; 37767</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22240; 37220</t>
+          <t>22623; 37699</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34262; 50731</t>
+          <t>35288; 50726</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8022; 16764</t>
+          <t>7896; 16776</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12305; 22148</t>
+          <t>12779; 22342</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13211; 23226</t>
+          <t>13772; 23718</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5609; 32605</t>
+          <t>6107; 32444</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10736; 20750</t>
+          <t>10725; 20345</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8988; 18059</t>
+          <t>9118; 18015</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5588; 13657</t>
+          <t>5674; 13727</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19169; 35303</t>
+          <t>19175; 34669</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21366; 34600</t>
+          <t>21023; 34124</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23731; 36248</t>
+          <t>23223; 36578</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21489; 34505</t>
+          <t>21745; 35114</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25592; 62860</t>
+          <t>23293; 61173</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32457; 49838</t>
+          <t>33713; 51225</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67876; 89891</t>
+          <t>67251; 90680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53571; 73725</t>
+          <t>53029; 73357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43225; 89984</t>
+          <t>43856; 89860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50167; 68950</t>
+          <t>50907; 68801</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64620; 86300</t>
+          <t>64064; 87054</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45230; 63813</t>
+          <t>44835; 63534</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>68245; 92357</t>
+          <t>67131; 91778</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87583; 113508</t>
+          <t>89310; 114590</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138008; 171072</t>
+          <t>138640; 172841</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104160; 132584</t>
+          <t>103391; 131952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>116988; 172684</t>
+          <t>113536; 171925</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40,54%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43,15%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>27,4%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>50,24%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>32,13%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53,99%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,38%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,22; 41,59</t>
+          <t>25,16; 55,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,22; 61,91</t>
+          <t>26,33; 49,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,57; 46,78</t>
+          <t>24,44; 54,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,91; 71,99</t>
+          <t>27,54; 57,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,8; 54,64</t>
+          <t>15,75; 41,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,55; 50,89</t>
+          <t>38,54; 61,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,68; 54,9</t>
+          <t>19,79; 46,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,42; 60,53</t>
+          <t>35,58; 72,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,68; 44,31</t>
+          <t>25,45; 44,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,29; 53,11</t>
+          <t>36,07; 52,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,12; 45,51</t>
+          <t>26,67; 45,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,52; 60,24</t>
+          <t>36,28; 60,94</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48,5%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>33,07%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>30,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>42,08%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,67%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,72; 45,72</t>
+          <t>34,41; 57,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 39,8</t>
+          <t>28,25; 46,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,93; 52,26</t>
+          <t>23,82; 46,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,82; 58,9</t>
+          <t>37,43; 61,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,58; 56,26</t>
+          <t>22,55; 45,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,77; 47,41</t>
+          <t>21,41; 40,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,23; 45,99</t>
+          <t>31,39; 52,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,16; 59,81</t>
+          <t>35,24; 59,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,73; 48,33</t>
+          <t>32,44; 48,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,6; 40,85</t>
+          <t>27,81; 41,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,1; 46,4</t>
+          <t>30,99; 46,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,98; 55,93</t>
+          <t>39,47; 57,24</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>35,57%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41,44%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38,77%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43,51%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29,78%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>44,38%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>29,05%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>61,35%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 46,91</t>
+          <t>20,33; 50,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,51; 56,48</t>
+          <t>28,39; 55,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,36; 40,68</t>
+          <t>26,32; 51,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,89; 73,7</t>
+          <t>30,53; 56,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,93; 51,26</t>
+          <t>16,42; 48,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,95; 56,29</t>
+          <t>31,47; 57,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,36; 51,51</t>
+          <t>19,1; 40,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,25; 58,05</t>
+          <t>48,58; 74,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,12; 44,63</t>
+          <t>22,41; 44,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 53,78</t>
+          <t>33,71; 53,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,09; 43,48</t>
+          <t>25,56; 41,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,35; 60,88</t>
+          <t>40,89; 61,3</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38,97%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34,23%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41,55%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>40,41%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>48,83%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>51,2%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,23%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,85; 54,93</t>
+          <t>27,89; 52,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,34; 63,54</t>
+          <t>26,55; 54,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,0; 65,45</t>
+          <t>20,98; 50,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 41,62</t>
+          <t>30,78; 54,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,19; 51,59</t>
+          <t>24,77; 53,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,0; 55,32</t>
+          <t>34,97; 63,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,98; 50,76</t>
+          <t>37,89; 65,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 53,59</t>
+          <t>26,58; 51,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,04; 48,76</t>
+          <t>30,42; 48,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,29; 54,01</t>
+          <t>35,41; 55,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,36; 55,49</t>
+          <t>34,02; 54,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 42,88</t>
+          <t>31,67; 48,26</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>32,96%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,9; 40,88</t>
+          <t>34,93; 47,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,84; 48,33</t>
+          <t>33,35; 45,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,48; 44,93</t>
+          <t>30,62; 44,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,68; 50,56</t>
+          <t>37,41; 51,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,37; 47,81</t>
+          <t>26,2; 40,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,24; 45,17</t>
+          <t>35,18; 47,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,42; 43,11</t>
+          <t>33,13; 45,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,84; 50,37</t>
+          <t>42,06; 55,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,17; 42,56</t>
+          <t>33,06; 42,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,45; 45,44</t>
+          <t>36,21; 44,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,28; 42,48</t>
+          <t>33,52; 42,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,55; 47,77</t>
+          <t>41,64; 50,97</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20083</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11885</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7523</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7954</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>24868</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>10056</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8629</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12023</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20083</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11885</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>15265</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4710; 12077</t>
+          <t>7462; 16478</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18919; 30644</t>
+          <t>13623; 25808</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6438; 14638</t>
+          <t>7376; 16366</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5580; 11506</t>
+          <t>4800; 10105</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7947; 16205</t>
+          <t>4572; 12053</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14257; 26334</t>
+          <t>19077; 30457</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8051; 16569</t>
+          <t>6192; 14548</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6801; 13533</t>
+          <t>5042; 10254</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14487; 26008</t>
+          <t>14935; 26188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36742; 53770</t>
+          <t>36526; 53005</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16057; 27976</t>
+          <t>16394; 28047</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14003; 23097</t>
+          <t>11465; 19258</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23461</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28521</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16420</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19997</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>14295</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19933</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>21807</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21716</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23461</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28521</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16420</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23264</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44980</t>
+          <t>39425</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9821; 19762</t>
+          <t>17535; 29521</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13968; 25969</t>
+          <t>21443; 35434</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16031; 27085</t>
+          <t>11281; 21939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15769; 27463</t>
+          <t>15433; 25297</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18132; 28672</t>
+          <t>9744; 19477</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21076; 35986</t>
+          <t>13972; 26578</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11475; 21782</t>
+          <t>16267; 27297</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17222; 29298</t>
+          <t>14410; 24394</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29879; 45514</t>
+          <t>30554; 45616</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38956; 57659</t>
+          <t>39250; 58249</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30845; 46021</t>
+          <t>30744; 46238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36316; 53469</t>
+          <t>32416; 47008</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8489</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13467</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16593</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19134</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6703</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>16742</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>12756</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22793</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8489</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13467</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16593</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>23618</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42873</t>
+          <t>42752</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3611; 10559</t>
+          <t>4851; 12107</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11887; 21310</t>
+          <t>9225; 18066</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8059; 17861</t>
+          <t>11267; 21991</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17791; 27379</t>
+          <t>13423; 25045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4757; 12234</t>
+          <t>3696; 10803</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8757; 18292</t>
+          <t>11875; 21816</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11709; 22044</t>
+          <t>8386; 17770</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13967; 26800</t>
+          <t>18435; 28129</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10722; 20696</t>
+          <t>10392; 20544</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23772; 37767</t>
+          <t>23675; 37318</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22623; 37699</t>
+          <t>22161; 36044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35288; 50726</t>
+          <t>33495; 50215</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15370</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9255</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25889</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>12343</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17168</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>18553</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18378</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15370</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13128</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9255</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27093</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>44745</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7896; 16776</t>
+          <t>10998; 20704</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12779; 22342</t>
+          <t>8646; 17719</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13772; 23718</t>
+          <t>5674; 13633</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6107; 32444</t>
+          <t>19182; 33961</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10725; 20345</t>
+          <t>7567; 16420</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9118; 18015</t>
+          <t>12295; 22306</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5674; 13727</t>
+          <t>13732; 23812</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19175; 34669</t>
+          <t>13285; 25648</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21023; 34124</t>
+          <t>21289; 34223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23223; 36578</t>
+          <t>23984; 37766</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21745; 35114</t>
+          <t>21529; 34610</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23293; 61173</t>
+          <t>35566; 54193</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>114</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>59343</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>72542</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>41295</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>78711</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>63172</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>59343</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75199</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>54153</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>151613</t>
+          <t>142186</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33713; 51225</t>
+          <t>50277; 68940</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67251; 90680</t>
+          <t>64263; 86818</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53029; 73357</t>
+          <t>45123; 65094</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43856; 89860</t>
+          <t>61711; 84667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50907; 68801</t>
+          <t>32833; 50167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64064; 87054</t>
+          <t>66003; 88793</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44835; 63534</t>
+          <t>54080; 73578</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67131; 91778</t>
+          <t>60145; 80004</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>89310; 114590</t>
+          <t>89012; 113480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138640; 172841</t>
+          <t>137731; 170864</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103391; 131952</t>
+          <t>104113; 131183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>113536; 171925</t>
+          <t>128241; 156954</t>
         </is>
       </c>
     </row>
